--- a/AAII_Financials/Yearly/DFNS_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/DFNS_YR_FIN.xlsx
@@ -1020,7 +1020,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-118100</v>
+        <v>-117800</v>
       </c>
       <c r="E20" s="3">
         <v>155400</v>
@@ -1050,7 +1050,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>88600</v>
+        <v>88300</v>
       </c>
       <c r="E21" s="3">
         <v>-159900</v>
@@ -1380,7 +1380,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>118100</v>
+        <v>117800</v>
       </c>
       <c r="E32" s="3">
         <v>-155400</v>
